--- a/data/trans_orig/Q04C1_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q04C1_2023-Habitat-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio que lleva residiendo en su vivienda</t>
+          <t>Tiempo medio que lleva residiendo en su vivienda (tasa de respuesta: 97,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,89; 24,15</t>
+          <t>20,81; 24,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,71; 26,29</t>
+          <t>23,79; 26,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,8; 24,87</t>
+          <t>22,75; 24,82</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,16; 20,66</t>
+          <t>18,23; 20,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,33; 22,42</t>
+          <t>20,32; 22,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19,6; 21,25</t>
+          <t>19,59; 21,26</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,97; 19,95</t>
+          <t>16,97; 19,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,4; 23,86</t>
+          <t>19,38; 23,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,81; 22,63</t>
+          <t>18,84; 22,68</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,8; 22,1</t>
+          <t>19,8; 22,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,29; 23,63</t>
+          <t>21,47; 23,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,97; 22,62</t>
+          <t>20,92; 22,62</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,58; 21,04</t>
+          <t>19,57; 20,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21,74; 23,28</t>
+          <t>21,77; 23,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20,98; 22,02</t>
+          <t>20,95; 22,1</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q04C1_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q04C1_2023-Habitat-trans_orig.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>22,52</t>
+          <t>21,86</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>25,01</t>
+          <t>24,49</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23,77</t>
+          <t>23,18</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,81; 24,12</t>
+          <t>20,09; 23,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,79; 26,26</t>
+          <t>23,25; 25,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,75; 24,82</t>
+          <t>22,15; 24,23</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19,41</t>
+          <t>18,89</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>21,35</t>
+          <t>20,8</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20,38</t>
+          <t>19,84</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,23; 20,76</t>
+          <t>17,82; 20,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,32; 22,45</t>
+          <t>19,66; 21,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19,59; 21,26</t>
+          <t>19,11; 20,68</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>18,4</t>
+          <t>17,64</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>21,7</t>
+          <t>19,35</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20,45</t>
+          <t>18,5</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,97; 19,77</t>
+          <t>16,24; 18,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,38; 23,78</t>
+          <t>18,19; 20,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,84; 22,68</t>
+          <t>17,55; 19,41</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>20,96</t>
+          <t>20,08</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>22,48</t>
+          <t>21,82</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21,76</t>
+          <t>21,0</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,8; 22,18</t>
+          <t>18,72; 21,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,47; 23,66</t>
+          <t>20,78; 22,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,92; 22,62</t>
+          <t>20,1; 21,81</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>20,3</t>
+          <t>19,57</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>22,43</t>
+          <t>21,55</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21,45</t>
+          <t>20,58</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,57; 20,98</t>
+          <t>18,91; 20,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21,77; 23,3</t>
+          <t>20,94; 22,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20,95; 22,1</t>
+          <t>20,15; 21,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q04C1_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q04C1_2023-Habitat-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio que lleva residiendo en su vivienda (tasa de respuesta: 97,78%)</t>
+          <t>Tiempo medio en años que lleva residiendo en su vivienda (tasa de respuesta: 97,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
